--- a/inst/ars-examples/ARS_dm_ae.xlsx
+++ b/inst/ars-examples/ARS_dm_ae.xlsx
@@ -11,13 +11,14 @@
     <sheet name="ReportingEvent" sheetId="2" r:id="rId2"/>
     <sheet name="MainListOfContents" sheetId="3" r:id="rId3"/>
     <sheet name="OtherListsOfContents" sheetId="4" r:id="rId4"/>
-    <sheet name="DataSubsets" sheetId="5" r:id="rId5"/>
-    <sheet name="AnalysisSets" sheetId="6" r:id="rId6"/>
-    <sheet name="AnalysisGroupings" sheetId="7" r:id="rId7"/>
-    <sheet name="Analyses" sheetId="8" r:id="rId8"/>
-    <sheet name="AnalysisMethods" sheetId="9" r:id="rId9"/>
-    <sheet name="AnalysisMethodCodeTemplate" sheetId="10" r:id="rId10"/>
-    <sheet name="AnalysisMethodCodeParameters" sheetId="11" r:id="rId11"/>
+    <sheet name="Outputs" sheetId="5" r:id="rId5"/>
+    <sheet name="DataSubsets" sheetId="6" r:id="rId6"/>
+    <sheet name="AnalysisSets" sheetId="7" r:id="rId7"/>
+    <sheet name="AnalysisGroupings" sheetId="8" r:id="rId8"/>
+    <sheet name="Analyses" sheetId="9" r:id="rId9"/>
+    <sheet name="AnalysisMethods" sheetId="10" r:id="rId10"/>
+    <sheet name="AnalysisMethodCodeTemplate" sheetId="11" r:id="rId11"/>
+    <sheet name="AnalysisMethodCodeParameters" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -384,7 +385,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ydisctools 0.0.231 build_ars()</t>
+          <t>ydisctools 0.0.233 build_ars()</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -404,6 +405,558 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>operation_id</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>operation_name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>operation_order</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>operation_label</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>operation_resultPattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mth_total_n</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Big N denominator count by group</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Total N (per group)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Distinct count of the analysis variable (typically USUBJID) per treatment group. Used as the N= header / denominator source. Verified against Common_Safety_Displays Mth01_CatVar_Count_ByGrp; current cards API.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Mth_total_n_op1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>xx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Summary of a continuous variable</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary_op1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>xx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Summary of a continuous variable</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary_op2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>xx.x</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Summary of a continuous variable</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary_op3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>(xx.xx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Summary of a continuous variable</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary_op4</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>xx.x</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Summary of a continuous variable</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary_op5</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>p25</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>xx.x</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Summary of a continuous variable</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary_op6</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>p75</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>xx.x</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Summary of a continuous variable</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary_op7</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>xx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Summary of a continuous variable</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Mth_continuous_summary_op8</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>xx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Summary of a categorical variable (n and %)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Categorical n (%)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>n and percentage of a categorical analysis variable per group, with a referenced denominator analysis and a data-driven/pre-defined grouping branch. Verified against Common_Safety_Displays Mth01_CatVar_Summ_ByGrp; current cards API. Spurious by_vars/strata_vars params from the legacy sheet have been dropped (the template uses by_listc).</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_op1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>xx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Summary of a categorical variable (n and %)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Categorical n (%)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>n and percentage of a categorical analysis variable per group, with a referenced denominator analysis and a data-driven/pre-defined grouping branch. Verified against Common_Safety_Displays Mth01_CatVar_Summ_ByGrp; current cards API. Spurious by_vars/strata_vars params from the legacy sheet have been dropped (the template uses by_listc).</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_op2</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>(xx.x)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -547,7 +1100,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1381,7 +1934,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1392,95 +1945,62 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>categoryIds</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>display1_Id</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>order</t>
+          <t>fileSpecification_file_name</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>compoundExpression_logicalOperator</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>condition_dataset</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>condition_variable</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>condition_comparator</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>condition_value</t>
+          <t>fileSpecification_file_location</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dss_01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>TRTEMFL EQ Y</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TRTEMFL EQ Y</t>
-        </is>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ADAE</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>TRTEMFL</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>Out_dm</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Summary of Demographic Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Out_ae</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Summary of Treatment-Emergent Adverse Events</t>
         </is>
       </c>
     </row>
@@ -1491,7 +2011,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1512,35 +2032,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>level</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>compoundExpression_logicalOperator</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>condition_dataset</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>condition_variable</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>condition_comparator</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>condition_value</t>
         </is>
@@ -1549,36 +2074,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AnalysisSet_01</t>
+          <t>Dss_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Safety Population</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>1</v>
+          <t>TRTEMFL EQ Y</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TRTEMFL EQ Y</t>
+        </is>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
+      <c r="F2">
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SAFFL</t>
+          <t>ADAE</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>TRTEMFL</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>EQ</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1591,7 +2121,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1607,438 +2137,80 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>groupingDataset</t>
+          <t>level</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>groupingVariable</t>
+          <t>order</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dataDriven</t>
+          <t>compoundExpression_logicalOperator</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>group_id</t>
+          <t>condition_dataset</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>group_name</t>
+          <t>condition_variable</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>group_label</t>
+          <t>condition_comparator</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>group_level</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>group_order</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>group_compoundExpression_logicalOperator</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>group_condition_dataset</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>group_condition_variable</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>group_condition_comparator</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>group_condition_value</t>
+          <t>condition_value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AnlsGrp_01_TRT01A</t>
+          <t>AnalysisSet_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TRT01A</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>Safety Population</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>ADSL</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>TRT01A</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>AnlsGrp_01_TRT01A_01</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Placebo</t>
+          <t>SAFFL</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Placebo</t>
-        </is>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>TRT01A</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
           <t>EQ</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Placebo</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AnlsGrp_01_TRT01A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TRT01A</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TRT01A</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>AnlsGrp_01_TRT01A_02</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>TRT01A</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Xanomeline Low Dose</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AnlsGrp_01_TRT01A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TRT01A</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TRT01A</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>AnlsGrp_01_TRT01A_03</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>TRT01A</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>EQ</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Xanomeline High Dose</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AnlsGrp_02_AGEGR1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AGEGR1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AGEGR1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AnlsGrp_03_SEX</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SEX</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>SEX</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AnlsGrp_04_RACE</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>RACE</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RACE</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AnlsGrp_05_AEBODSYS</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AEBODSYS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ADAE</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AEBODSYS</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AnlsGrp_06_AEDECOD</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>AEDECOD</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ADAE</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AEDECOD</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AnlsGrp_07_AESEV</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>AESEV</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ADAE</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AESEV</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2221,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2060,125 +2232,125 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>label</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>categoryIds</t>
+          <t>groupingDataset</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>groupingVariable</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>purpose</t>
+          <t>dataDriven</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>analysisSetId</t>
+          <t>group_id</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>groupingId1</t>
+          <t>group_name</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>resultsByGroup1</t>
+          <t>group_label</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>groupingId2</t>
+          <t>group_level</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>resultsByGroup2</t>
+          <t>group_order</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dataSubsetId</t>
+          <t>group_compoundExpression_logicalOperator</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dataset</t>
+          <t>group_condition_dataset</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>variable</t>
+          <t>group_condition_variable</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>method_id</t>
+          <t>group_condition_comparator</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>referencedAnalysisOperations_referencedOperationId1</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>referencedAnalysisOperations_analysisId1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>referencedAnalysisOperations_referencedOperationId2</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>referencedAnalysisOperations_analysisId2</t>
+          <t>group_condition_value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>An_01</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Number of subjects</t>
+          <t>AnlsGrp_01_TRT01A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TRT01A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SPECIFIED IN SAP</t>
+          <t>TRT01A</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AnalysisSet_01</t>
+          <t>AnlsGrp_01_TRT01A_01</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AnlsGrp_01_TRT01A</t>
-        </is>
-      </c>
-      <c r="I2" t="b">
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
         <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
@@ -2188,46 +2360,66 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>USUBJID</t>
+          <t>TRT01A</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Mth_total_n</t>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Placebo</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>An_02</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Age (years)</t>
+          <t>AnlsGrp_01_TRT01A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TRT01A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SPECIFIED IN SAP</t>
+          <t>TRT01A</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AnalysisSet_01</t>
+          <t>AnlsGrp_01_TRT01A_02</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AnlsGrp_01_TRT01A</t>
-        </is>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -2236,54 +2428,66 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>AGE</t>
+          <t>TRT01A</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Mth_continuous_summary</t>
+          <t>EQ</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>An_03</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Age group, n (%)</t>
+          <t>AnlsGrp_01_TRT01A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TRT01A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SPECIFIED IN SAP</t>
+          <t>TRT01A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AnalysisSet_01</t>
+          <t>AnlsGrp_01_TRT01A_03</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AnlsGrp_01_TRT01A</t>
-        </is>
-      </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>AnlsGrp_02_AGEGR1</t>
-        </is>
-      </c>
-      <c r="K4" t="b">
-        <v>1</v>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -2292,548 +2496,179 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>USUBJID</t>
+          <t>TRT01A</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary</t>
+          <t>EQ</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_num</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>An_03</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_pct_den</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>An_01</t>
+          <t>Xanomeline High Dose</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>An_04</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Sex, n (%)</t>
+          <t>AnlsGrp_02_AGEGR1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AGEGR1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SPECIFIED IN SAP</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>AnalysisSet_01</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>AnlsGrp_01_TRT01A</t>
-        </is>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>AnlsGrp_03_SEX</t>
-        </is>
-      </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>USUBJID</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_pct_num</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>An_04</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_pct_den</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>An_01</t>
+          <t>AGEGR1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>An_05</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Race, n (%)</t>
+          <t>AnlsGrp_03_SEX</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SEX</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SPECIFIED IN SAP</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AnalysisSet_01</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>AnlsGrp_01_TRT01A</t>
-        </is>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>AnlsGrp_04_RACE</t>
-        </is>
-      </c>
-      <c r="K6" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>USUBJID</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_pct_num</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>An_05</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_pct_den</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>An_01</t>
+          <t>SEX</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>An_06</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Number of subjects</t>
+          <t>AnlsGrp_04_RACE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RACE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SPECIFIED IN SAP</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>AnalysisSet_01</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>AnlsGrp_01_TRT01A</t>
-        </is>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>ADSL</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>USUBJID</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Mth_total_n</t>
+          <t>RACE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>An_07</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Subjects with at least one TEAE, n (%)</t>
+          <t>AnlsGrp_05_AEBODSYS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AEBODSYS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ADAE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SPECIFIED IN SAP</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>AnalysisSet_01</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>AnlsGrp_01_TRT01A</t>
-        </is>
-      </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Dss_01</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>ADAE</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>USUBJID</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_pct_num</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>An_07</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_pct_den</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>An_06</t>
+          <t>AEBODSYS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>An_08</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TEAE by System Organ Class, n (%)</t>
+          <t>AnlsGrp_06_AEDECOD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AEDECOD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ADAE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SPECIFIED IN SAP</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>AnalysisSet_01</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>AnlsGrp_01_TRT01A</t>
-        </is>
-      </c>
-      <c r="I9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>AnlsGrp_05_AEBODSYS</t>
-        </is>
-      </c>
-      <c r="K9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Dss_01</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>ADAE</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>USUBJID</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_pct_num</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>An_08</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_pct_den</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>An_06</t>
+          <t>AEDECOD</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>An_09</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TEAE by Preferred Term, n (%)</t>
+          <t>AnlsGrp_07_AESEV</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AESEV</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ADAE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SPECIFIED IN SAP</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>AnalysisSet_01</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>AnlsGrp_01_TRT01A</t>
-        </is>
-      </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>AnlsGrp_06_AEDECOD</t>
-        </is>
-      </c>
-      <c r="K10" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Dss_01</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>ADAE</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>USUBJID</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_pct_num</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>An_09</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_pct_den</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>An_06</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>An_10</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>TEAE by severity, n (%)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>SPECIFIED IN SAP</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AnalysisSet_01</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>AnlsGrp_01_TRT01A</t>
-        </is>
-      </c>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>AnlsGrp_07_AESEV</t>
-        </is>
-      </c>
-      <c r="K11" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Dss_01</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>ADAE</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>USUBJID</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_pct_num</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>An_10</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_pct_den</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>An_06</t>
+          <t>AESEV</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2679,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2855,537 +2690,780 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>categoryIds</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>operation_id</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>operation_name</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>operation_order</t>
+          <t>analysisSetId</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>operation_label</t>
+          <t>groupingId1</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>operation_resultPattern</t>
+          <t>resultsByGroup1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>groupingId2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>resultsByGroup2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dataSubsetId</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dataset</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>method_id</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>referencedAnalysisOperations_referencedOperationId1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>referencedAnalysisOperations_analysisId1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>referencedAnalysisOperations_referencedOperationId2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>referencedAnalysisOperations_analysisId2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>An_01</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Number of subjects</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>AnalysisSet_01</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>AnlsGrp_01_TRT01A</t>
+        </is>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>Mth_total_n</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Big N denominator count by group</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Total N (per group)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Distinct count of the analysis variable (typically USUBJID) per treatment group. Used as the N= header / denominator source. Verified against Common_Safety_Displays Mth01_CatVar_Count_ByGrp; current cards API.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mth_total_n_op1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>xx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>An_02</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Age (years)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>AnalysisSet_01</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AnlsGrp_01_TRT01A</t>
+        </is>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>AGE</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>Mth_continuous_summary</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Summary of a continuous variable</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Mth_continuous_summary_op1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>xx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mth_continuous_summary</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Summary of a continuous variable</t>
-        </is>
+          <t>An_03</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
+          <t>Age group, n (%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mth_continuous_summary_op2</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>2</v>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AnalysisSet_01</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>xx.x</t>
+          <t>AnlsGrp_01_TRT01A</t>
+        </is>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>AnlsGrp_02_AGEGR1</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_num</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>An_03</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_den</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>An_01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mth_continuous_summary</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Summary of a continuous variable</t>
-        </is>
+          <t>An_04</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
+          <t>Sex, n (%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mth_continuous_summary_op3</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="G5">
-        <v>3</v>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AnalysisSet_01</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>(xx.xx)</t>
+          <t>AnlsGrp_01_TRT01A</t>
+        </is>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>AnlsGrp_03_SEX</t>
+        </is>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_num</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>An_04</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_den</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>An_01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mth_continuous_summary</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Summary of a continuous variable</t>
-        </is>
+          <t>An_05</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
+          <t>Race, n (%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mth_continuous_summary_op4</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-      <c r="G6">
-        <v>4</v>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AnalysisSet_01</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Median</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>xx.x</t>
+          <t>AnlsGrp_01_TRT01A</t>
+        </is>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>AnlsGrp_04_RACE</t>
+        </is>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_num</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>An_05</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_den</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>An_01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mth_continuous_summary</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Summary of a continuous variable</t>
-        </is>
+          <t>An_06</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
+          <t>Number of subjects</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mth_continuous_summary_op5</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>p25</t>
-        </is>
-      </c>
-      <c r="G7">
-        <v>5</v>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>AnalysisSet_01</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>xx.x</t>
+          <t>AnlsGrp_01_TRT01A</t>
+        </is>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ADSL</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Mth_total_n</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mth_continuous_summary</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Summary of a continuous variable</t>
-        </is>
+          <t>An_07</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
+          <t>Subjects with at least one TEAE, n (%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mth_continuous_summary_op6</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>p75</t>
-        </is>
-      </c>
-      <c r="G8">
-        <v>6</v>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>AnalysisSet_01</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>xx.x</t>
+          <t>AnlsGrp_01_TRT01A</t>
+        </is>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Dss_01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_num</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>An_07</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_den</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>An_06</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mth_continuous_summary</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Summary of a continuous variable</t>
-        </is>
+          <t>An_08</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
+          <t>TEAE by System Organ Class, n (%)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mth_continuous_summary_op7</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="G9">
-        <v>7</v>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>AnalysisSet_01</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>xx</t>
+          <t>AnlsGrp_01_TRT01A</t>
+        </is>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>AnlsGrp_05_AEBODSYS</t>
+        </is>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Dss_01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_num</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>An_08</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_den</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>An_06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mth_continuous_summary</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Summary of a continuous variable</t>
-        </is>
+          <t>An_09</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Continuous summary (N, mean, SD, median, Q1, Q3, min, max)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Descriptive statistics of a continuous analysis variable per group. Verified against Common_Safety_Displays Mth02_ContVar_Summ_ByGrp; current cards API (ard_summary, by_listc). Fixes the legacy sheet which used the deprecated ard_continuous + by_stmt (the latter stamps no group metadata).</t>
+          <t>TEAE by Preferred Term, n (%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mth_continuous_summary_op8</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
-      </c>
-      <c r="G10">
-        <v>8</v>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AnalysisSet_01</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>xx</t>
+          <t>AnlsGrp_01_TRT01A</t>
+        </is>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>AnlsGrp_06_AEDECOD</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Dss_01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_num</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>An_09</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_den</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>An_06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>An_10</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TEAE by severity, n (%)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AnalysisSet_01</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>AnlsGrp_01_TRT01A</t>
+        </is>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AnlsGrp_07_AESEV</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Dss_01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>Mth_categorical_summary</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Summary of a categorical variable (n and %)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Categorical n (%)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>n and percentage of a categorical analysis variable per group, with a referenced denominator analysis and a data-driven/pre-defined grouping branch. Verified against Common_Safety_Displays Mth01_CatVar_Summ_ByGrp; current cards API. Spurious by_vars/strata_vars params from the legacy sheet have been dropped (the template uses by_listc).</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_op1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>xx</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Summary of a categorical variable (n and %)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Categorical n (%)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>n and percentage of a categorical analysis variable per group, with a referenced denominator analysis and a data-driven/pre-defined grouping branch. Verified against Common_Safety_Displays Mth01_CatVar_Summ_ByGrp; current cards API. Spurious by_vars/strata_vars params from the legacy sheet have been dropped (the template uses by_listc).</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_op2</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>(xx.x)</t>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_num</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>An_10</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_den</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>An_06</t>
         </is>
       </c>
     </row>

--- a/inst/ars-examples/ARS_dm_ae.xlsx
+++ b/inst/ars-examples/ARS_dm_ae.xlsx
@@ -385,7 +385,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ydisctools 0.0.233 build_ars()</t>
+          <t>ydisctools 0.0.234 build_ars()</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>n and percentage of a categorical analysis variable per group, with a referenced denominator analysis and a data-driven/pre-defined grouping branch. Verified against Common_Safety_Displays Mth01_CatVar_Summ_ByGrp; current cards API. Spurious by_vars/strata_vars params from the legacy sheet have been dropped (the template uses by_listc).</t>
+          <t>Distinct-subject n and percentage per category and group, with a referenced denominator analysis. Modern cards pattern: the category variable is passed as `variables=` (so it lands in the ARD's variable / variable_level columns) and the outer grouping(s) as `by=` (`strata=` when the innermost grouping is data-driven). ydisctools overlay entry; replaces the siera catalog's distinct+dummy template.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>n and percentage of a categorical analysis variable per group, with a referenced denominator analysis and a data-driven/pre-defined grouping branch. Verified against Common_Safety_Displays Mth01_CatVar_Summ_ByGrp; current cards API. Spurious by_vars/strata_vars params from the legacy sheet have been dropped (the template uses by_listc).</t>
+          <t>Distinct-subject n and percentage per category and group, with a referenced denominator analysis. Modern cards pattern: the category variable is passed as `variables=` (so it lands in the ARD's variable / variable_level columns) and the outer grouping(s) as `by=` (`strata=` when the innermost grouping is data-driven). ydisctools overlay entry; replaces the siera catalog's distinct+dummy template.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1070,25 +1070,22 @@
           <t>denom_dataset = df2_denomanaidhere |&gt;
   dplyr::select(denom_anagroupvarshere)
 in_data = df2_analysisidhere |&gt;
-    dplyr::distinct(distinctlisthere) |&gt;
-    dplyr::mutate(dummy = 'dummyvar')
+    dplyr::distinct(distinctlisthere)
 dataDriven = isdatadrivenhere
 if(dataDriven == TRUE){
 df3_analysisidhere &lt;-
   cards::ard_tabulate(
-    data = in_data,
-    strata = c(byvarshere),
-    variables = 'dummy',
+    data = in_data
+    stratavarshere,
     denominator = denom_dataset
   ) } else {
 df3_analysisidhere &lt;-
  cards::ard_tabulate(
-    data = in_data,
-    by = c(byvarshere),
-    variables = 'dummy',
+    data = in_data
+    byvarshere,
     denominator = denom_dataset
   ) }
-df3_analysisidhere &lt;- df3_analysisidhere|&gt;
+df3_analysisidhere &lt;- df3_analysisidhere |&gt;
   dplyr::filter(stat_name %in% c('n', 'p')) |&gt;
   dplyr::mutate(operationid = dplyr::case_when(stat_name == 'n' ~ 'opid1here',
                                                stat_name == 'p' ~ 'opid2here'))</t>
@@ -1102,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1393,17 +1390,44 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Grouping variables as a quoted, comma-separated list</t>
+          <t>by = outer grouping(s), variables = category variable</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>by vars (list)</t>
+          <t>by/variables args</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>by_listc</t>
+          <t>by_vars</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>stratavarshere</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>strata = outer grouping(s), variables = category variable</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>strata/variables args</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>strata_vars</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1472,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1588,7 +1612,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Age group, n (%)</t>
+          <t>Age group 1, n (%)</t>
         </is>
       </c>
       <c r="E5">
@@ -1616,7 +1640,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sex, n (%)</t>
+          <t>Age group 2, n (%)</t>
         </is>
       </c>
       <c r="E6">
@@ -1644,7 +1668,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Race, n (%)</t>
+          <t>Sex, n (%)</t>
         </is>
       </c>
       <c r="E7">
@@ -1668,19 +1692,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Summary of Treatment-Emergent Adverse Events</t>
+          <t>Race, n (%)</t>
         </is>
       </c>
       <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Out_ae</t>
+        <v>6</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>An_06</t>
         </is>
       </c>
     </row>
@@ -1700,15 +1724,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Number of subjects</t>
+          <t>Ethnicity, n (%)</t>
         </is>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>An_06</t>
+          <t>An_07</t>
         </is>
       </c>
     </row>
@@ -1724,19 +1748,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Subjects with at least one TEAE, n (%)</t>
+          <t>Summary of Treatment-Emergent Adverse Events</t>
         </is>
       </c>
       <c r="E10">
         <v>2</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>An_07</t>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Out_ae</t>
         </is>
       </c>
     </row>
@@ -1756,11 +1780,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TEAE by System Organ Class, n (%)</t>
+          <t>Number of subjects</t>
         </is>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1784,11 +1808,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TEAE by Preferred Term, n (%)</t>
+          <t>Subjects with at least one TEAE, n (%)</t>
         </is>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1812,15 +1836,71 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TEAE by System Organ Class, n (%)</t>
+        </is>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>An_10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>List of Planned Analyses</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LOPA</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TEAE by Preferred Term, n (%)</t>
+        </is>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>An_11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>List of Planned Analyses</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LOPA</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>TEAE by severity, n (%)</t>
         </is>
       </c>
-      <c r="E13">
+      <c r="E15">
         <v>5</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>An_10</t>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>An_12</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2301,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2540,12 +2620,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AnlsGrp_03_SEX</t>
+          <t>AnlsGrp_03_AGEGR2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>AGEGR2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2555,7 +2635,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>AGEGR2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2567,12 +2647,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AnlsGrp_04_RACE</t>
+          <t>AnlsGrp_04_SEX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2582,7 +2662,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2594,22 +2674,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AnlsGrp_05_AEBODSYS</t>
+          <t>AnlsGrp_05_RACE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AEBODSYS</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ADAE</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AEBODSYS</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2621,22 +2701,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AnlsGrp_06_AEDECOD</t>
+          <t>AnlsGrp_06_ETHNIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AEDECOD</t>
+          <t>ETHNIC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ADAE</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AEDECOD</t>
+          <t>ETHNIC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2648,25 +2728,79 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AnlsGrp_07_AESEV</t>
+          <t>AnlsGrp_07_AEBODSYS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>AEBODSYS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AEBODSYS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AnlsGrp_08_AEDECOD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AEDECOD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AEDECOD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AnlsGrp_09_AESEV</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>AESEV</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>ADAE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>AESEV</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -2679,7 +2813,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2886,7 +3020,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Age group, n (%)</t>
+          <t>Age group 1, n (%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2962,7 +3096,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sex, n (%)</t>
+          <t>Age group 2, n (%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2985,7 +3119,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AnlsGrp_03_SEX</t>
+          <t>AnlsGrp_03_AGEGR2</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -3038,7 +3172,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Race, n (%)</t>
+          <t>Sex, n (%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3061,7 +3195,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AnlsGrp_04_RACE</t>
+          <t>AnlsGrp_04_SEX</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -3114,7 +3248,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Number of subjects</t>
+          <t>Race, n (%)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3135,6 +3269,14 @@
       <c r="I7" t="b">
         <v>1</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>AnlsGrp_05_RACE</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>ADSL</t>
@@ -3147,7 +3289,27 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Mth_total_n</t>
+          <t>Mth_categorical_summary</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_num</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>An_06</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_den</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>An_01</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3324,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Subjects with at least one TEAE, n (%)</t>
+          <t>Ethnicity, n (%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3183,14 +3345,17 @@
       <c r="I8" t="b">
         <v>1</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Dss_01</t>
-        </is>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>AnlsGrp_06_ETHNIC</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ADAE</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -3220,7 +3385,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>An_06</t>
+          <t>An_01</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3400,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TEAE by System Organ Class, n (%)</t>
+          <t>Number of subjects</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3256,22 +3421,9 @@
       <c r="I9" t="b">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>AnlsGrp_05_AEBODSYS</t>
-        </is>
-      </c>
-      <c r="K9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Dss_01</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>ADAE</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -3281,27 +3433,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_pct_num</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>An_08</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Mth_categorical_summary_pct_den</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>An_06</t>
+          <t>Mth_total_n</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3448,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TEAE by Preferred Term, n (%)</t>
+          <t>Subjects with at least one TEAE, n (%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3337,14 +3469,6 @@
       <c r="I10" t="b">
         <v>1</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>AnlsGrp_06_AEDECOD</t>
-        </is>
-      </c>
-      <c r="K10" t="b">
-        <v>1</v>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>Dss_01</t>
@@ -3382,7 +3506,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>An_06</t>
+          <t>An_08</t>
         </is>
       </c>
     </row>
@@ -3397,73 +3521,235 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>TEAE by System Organ Class, n (%)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AnalysisSet_01</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>AnlsGrp_01_TRT01A</t>
+        </is>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AnlsGrp_07_AEBODSYS</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Dss_01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_num</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>An_10</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_den</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>An_08</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>An_11</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TEAE by Preferred Term, n (%)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SPECIFIED IN SAP</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AnalysisSet_01</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AnlsGrp_01_TRT01A</t>
+        </is>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>AnlsGrp_08_AEDECOD</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Dss_01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ADAE</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_num</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>An_11</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_pct_den</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>An_08</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>An_12</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>TEAE by severity, n (%)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>SPECIFIED IN SAP</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>AnalysisSet_01</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>AnlsGrp_01_TRT01A</t>
         </is>
       </c>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>AnlsGrp_07_AESEV</t>
-        </is>
-      </c>
-      <c r="K11" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>AnlsGrp_09_AESEV</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>Dss_01</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>ADAE</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>USUBJID</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Mth_categorical_summary</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>Mth_categorical_summary_pct_num</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>An_10</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>An_12</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>Mth_categorical_summary_pct_den</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>An_06</t>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>An_08</t>
         </is>
       </c>
     </row>

--- a/inst/ars-examples/ARS_dm_ae.xlsx
+++ b/inst/ars-examples/ARS_dm_ae.xlsx
@@ -385,7 +385,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ydisctools 0.0.234 build_ars()</t>
+          <t>ydisctools 0.0.240 build_ars()</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Distinct-subject n and percentage per category and group, with a referenced denominator analysis. Modern cards pattern: the category variable is passed as `variables=` (so it lands in the ARD's variable / variable_level columns) and the outer grouping(s) as `by=` (`strata=` when the innermost grouping is data-driven). ydisctools overlay entry; replaces the siera catalog's distinct+dummy template.</t>
+          <t>Distinct-subject n and percentage per category and group, with a referenced denominator analysis. Modern cards pattern: the category variable is passed as `variables=` (so it lands in the ARD's variable / variable_level columns) and the outer grouping(s) as `by=` (`strata=` when the innermost grouping is data-driven). A flat analysis (no category variable, e.g. 'subjects with at least one TEAE') tabulates a constant flag with the group as `by=`, so the percentage denominator is the per-group big N rather than the overall N. ydisctools overlay entry; replaces the siera catalog's distinct+dummy template.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Distinct-subject n and percentage per category and group, with a referenced denominator analysis. Modern cards pattern: the category variable is passed as `variables=` (so it lands in the ARD's variable / variable_level columns) and the outer grouping(s) as `by=` (`strata=` when the innermost grouping is data-driven). ydisctools overlay entry; replaces the siera catalog's distinct+dummy template.</t>
+          <t>Distinct-subject n and percentage per category and group, with a referenced denominator analysis. Modern cards pattern: the category variable is passed as `variables=` (so it lands in the ARD's variable / variable_level columns) and the outer grouping(s) as `by=` (`strata=` when the innermost grouping is data-driven). A flat analysis (no category variable, e.g. 'subjects with at least one TEAE') tabulates a constant flag with the group as `by=`, so the percentage denominator is the per-group big N rather than the overall N. ydisctools overlay entry; replaces the siera catalog's distinct+dummy template.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1072,7 +1072,15 @@
 in_data = df2_analysisidhere |&gt;
     dplyr::distinct(distinctlisthere)
 dataDriven = isdatadrivenhere
-if(dataDriven == TRUE){
+if(ncol(in_data) &lt;= 2){
+# flat analysis (no category variable): tabulate a constant flag with the
+# group as `by`, so the percentage denominator is the per-group big N
+df3_analysisidhere &lt;-
+  cards::ard_tabulate(
+    data = in_data |&gt; dplyr::mutate(.flag_ = 'Y')
+    , by = 'denom_anagroupvarshere', variables = '.flag_',
+    denominator = denom_dataset
+  ) } else if(dataDriven == TRUE){
 df3_analysisidhere &lt;-
   cards::ard_tabulate(
     data = in_data

--- a/inst/ars-examples/ARS_dm_ae.xlsx
+++ b/inst/ars-examples/ARS_dm_ae.xlsx
@@ -385,7 +385,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ydisctools 0.0.240 build_ars()</t>
+          <t>ydisctools 0.0.244 build_ars()</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -406,7 +406,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -879,7 +879,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Distinct-subject n and percentage per category and group, with a referenced denominator analysis. Modern cards pattern: the category variable is passed as `variables=` (so it lands in the ARD's variable / variable_level columns) and the outer grouping(s) as `by=` (`strata=` when the innermost grouping is data-driven). A flat analysis (no category variable, e.g. 'subjects with at least one TEAE') tabulates a constant flag with the group as `by=`, so the percentage denominator is the per-group big N rather than the overall N. ydisctools overlay entry; replaces the siera catalog's distinct+dummy template.</t>
+          <t>Distinct-subject n and percentage per category and group, with a referenced denominator analysis. Modern cards pattern: the category variable is passed as `variables=` (so it lands in the ARD's variable / variable_level columns) and the outer grouping(s) as `by=` (`strata=` when the innermost grouping is data-driven). Flat analyses (no category variable) are generated from the dedicated categorical_summary_flat template instead. ydisctools overlay entry; replaces the siera catalog's distinct+dummy template.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Distinct-subject n and percentage per category and group, with a referenced denominator analysis. Modern cards pattern: the category variable is passed as `variables=` (so it lands in the ARD's variable / variable_level columns) and the outer grouping(s) as `by=` (`strata=` when the innermost grouping is data-driven). A flat analysis (no category variable, e.g. 'subjects with at least one TEAE') tabulates a constant flag with the group as `by=`, so the percentage denominator is the per-group big N rather than the overall N. ydisctools overlay entry; replaces the siera catalog's distinct+dummy template.</t>
+          <t>Distinct-subject n and percentage per category and group, with a referenced denominator analysis. Modern cards pattern: the category variable is passed as `variables=` (so it lands in the ARD's variable / variable_level columns) and the outer grouping(s) as `by=` (`strata=` when the innermost grouping is data-driven). Flat analyses (no category variable) are generated from the dedicated categorical_summary_flat template instead. ydisctools overlay entry; replaces the siera catalog's distinct+dummy template.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -946,6 +946,96 @@
         </is>
       </c>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>(xx.x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Subject count per group (n and %)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Flat n (%)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Distinct-subject n and percentage per group for a flat analysis (no category variable, e.g. 'subjects with at least one TEAE'), with a referenced denominator analysis. Tabulates a constant '.flag_' with the group as `by=`, so the percentage denominator is that group's big N. Selected automatically by build_ars() when a categorical_summary analysis has a single grouping and variable = USUBJID; the compact parameter format keeps the categorical_summary key. ydisctools overlay entry.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat_op1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>xx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Subject count per group (n and %)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Flat n (%)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Distinct-subject n and percentage per group for a flat analysis (no category variable, e.g. 'subjects with at least one TEAE'), with a referenced denominator analysis. Tabulates a constant '.flag_' with the group as `by=`, so the percentage denominator is that group's big N. Selected automatically by build_ars() when a categorical_summary analysis has a single grouping and variable = USUBJID; the compact parameter format keeps the categorical_summary key. ydisctools overlay entry.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat_op2</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>(xx.x)</t>
         </is>
@@ -958,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1071,16 +1161,9 @@
   dplyr::select(denom_anagroupvarshere)
 in_data = df2_analysisidhere |&gt;
     dplyr::distinct(distinctlisthere)
+# strata= when the innermost grouping is data-driven, by= when pre-defined
 dataDriven = isdatadrivenhere
-if(ncol(in_data) &lt;= 2){
-# flat analysis (no category variable): tabulate a constant flag with the
-# group as `by`, so the percentage denominator is the per-group big N
-df3_analysisidhere &lt;-
-  cards::ard_tabulate(
-    data = in_data |&gt; dplyr::mutate(.flag_ = 'Y')
-    , by = 'denom_anagroupvarshere', variables = '.flag_',
-    denominator = denom_dataset
-  ) } else if(dataDriven == TRUE){
+if(dataDriven == TRUE){
 df3_analysisidhere &lt;-
   cards::ard_tabulate(
     data = in_data
@@ -1100,6 +1183,44 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>R (siera)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>denom_dataset = df2_denomanaidhere |&gt;
+  dplyr::select(denom_anagroupvarshere)
+# n (%) of subjects per group: tabulate a constant flag with the group as
+# `by`, so the percentage denominator is that group's big N
+in_data = df2_analysisidhere |&gt;
+    dplyr::distinct(distinctlisthere) |&gt;
+    dplyr::mutate(.flag_ = 'Y')
+df3_analysisidhere &lt;-
+  cards::ard_tabulate(
+    data = in_data
+    , by = 'denom_anagroupvarshere', variables = '.flag_',
+    denominator = denom_dataset
+  )
+df3_analysisidhere &lt;- df3_analysisidhere |&gt;
+  dplyr::filter(stat_name %in% c('n', 'p')) |&gt;
+  dplyr::mutate(operationid = dplyr::case_when(stat_name == 'n' ~ 'opid1here',
+                                               stat_name == 'p' ~ 'opid2here'))</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1107,7 +1228,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1436,6 +1557,87 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>strata_vars</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>distinctlisthere</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Grouping variable + analysis variable, comma separated</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>distinct list</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>distinct_list</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>denomanaidhere</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Analysis ID supplying the denominator</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>denom ana id</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DEN_analysisid</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Mth_categorical_summary_flat</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>denom_anagroupvarshere</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Grouping variable of the denominator analysis</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>denom grp var</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AG_denom_var1</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3696,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary</t>
+          <t>Mth_categorical_summary_flat</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_num</t>
+          <t>Mth_categorical_summary_flat_pct_num</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -3509,7 +3711,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Mth_categorical_summary_pct_den</t>
+          <t>Mth_categorical_summary_flat_pct_den</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
